--- a/2023/NEI/tables/Section-0/acronyms.xlsx
+++ b/2023/NEI/tables/Section-0/acronyms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/seltzer_karl_epa_gov1/Documents/Profile/Documents/GitHub/EIB-TSD_dev/2023/NEI/tables/Section-0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usepa-my.sharepoint.com/personal/seltzer_karl_epa_gov1/Documents/Documents/GitHub/EIB-TSD_dev/2023/NEI/tables/Section-0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="13_ncr:1_{1E4CBF0D-116D-4626-9802-D581C2A682E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CEA457F-0CC2-4580-A02F-65F2F6203353}"/>
+  <xr:revisionPtr revIDLastSave="251" documentId="13_ncr:1_{1E4CBF0D-116D-4626-9802-D581C2A682E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DC6D385-77BC-42F8-9A50-F91D8A6A6477}"/>
   <bookViews>
-    <workbookView xWindow="-17325" yWindow="540" windowWidth="15210" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24450" yWindow="690" windowWidth="22485" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -689,9 +689,6 @@
     <t>S/L/T</t>
   </si>
   <si>
-    <t>State, local, and tribal (agencies)</t>
-  </si>
-  <si>
     <t>SMARTFIRE</t>
   </si>
   <si>
@@ -1479,6 +1476,9 @@
   </si>
   <si>
     <t>Pile Burn</t>
+  </si>
+  <si>
+    <t>State, local, and Tribal (agencies)</t>
   </si>
 </sst>
 </file>
@@ -1514,13 +1514,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1808,42 +1804,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B1" t="s">
         <v>247</v>
-      </c>
-      <c r="B1" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1858,16 +1854,16 @@
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>393</v>
+        <v>257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1880,18 +1876,18 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1904,26 +1900,26 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1968,10 +1964,10 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1984,18 +1980,18 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2008,10 +2004,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2040,10 +2036,10 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2064,10 +2060,10 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2104,10 +2100,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2120,10 +2116,10 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2136,34 +2132,34 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2176,10 +2172,10 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2187,7 +2183,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2202,7 +2198,7 @@
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2219,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2240,18 +2236,18 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>412</v>
+        <v>275</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>413</v>
+        <v>276</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2264,26 +2260,26 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>414</v>
+        <v>277</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2328,34 +2324,34 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2368,50 +2364,50 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>420</v>
+        <v>283</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>424</v>
+        <v>287</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2424,97 +2420,97 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>427</v>
+        <v>290</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2536,10 +2532,10 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>433</v>
+        <v>296</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2552,26 +2548,26 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2584,25 +2580,25 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2616,49 +2612,49 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>439</v>
+        <v>302</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>442</v>
+        <v>305</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2674,16 +2670,16 @@
       <c r="A109" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2712,18 +2708,18 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2760,42 +2756,42 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -2832,18 +2828,18 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -2856,18 +2852,18 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -2896,17 +2892,17 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" t="s">
         <v>136</v>
       </c>
     </row>
@@ -2920,10 +2916,10 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -2936,42 +2932,42 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>457</v>
+        <v>320</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>458</v>
+        <v>321</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -2984,26 +2980,26 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>462</v>
+        <v>325</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3016,34 +3012,34 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>464</v>
+        <v>327</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>329</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>465</v>
+        <v>328</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>464</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>330</v>
-      </c>
-      <c r="B154" s="3" t="s">
-        <v>466</v>
+        <v>329</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>331</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>467</v>
+        <v>330</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3056,10 +3052,10 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>332</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>468</v>
+        <v>331</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3088,10 +3084,10 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B161" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3104,18 +3100,18 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B163" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B164" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3144,18 +3140,18 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B168" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B169" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3168,10 +3164,10 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B171" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3184,10 +3180,10 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B173" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3216,10 +3212,10 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B177" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3232,10 +3228,10 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B179" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3248,18 +3244,18 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B181" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B182" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3352,10 +3348,10 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B194" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3368,10 +3364,10 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B196" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3384,18 +3380,18 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B198" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B199" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3408,10 +3404,10 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B201" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3432,10 +3428,10 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B204" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3456,10 +3452,10 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B207" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3472,10 +3468,10 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B209" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3483,271 +3479,271 @@
         <v>215</v>
       </c>
       <c r="B210" t="s">
-        <v>216</v>
+        <v>479</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>216</v>
+      </c>
+      <c r="B211" t="s">
         <v>217</v>
-      </c>
-      <c r="B211" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" t="s">
         <v>219</v>
-      </c>
-      <c r="B212" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" t="s">
         <v>221</v>
-      </c>
-      <c r="B213" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
+        <v>222</v>
+      </c>
+      <c r="B214" t="s">
         <v>223</v>
-      </c>
-      <c r="B214" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B215" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B216" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" t="s">
         <v>225</v>
-      </c>
-      <c r="B217" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B218" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B219" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B220" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B221" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>226</v>
+      </c>
+      <c r="B222" t="s">
         <v>227</v>
-      </c>
-      <c r="B222" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B223" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>228</v>
+      </c>
+      <c r="B224" t="s">
         <v>229</v>
-      </c>
-      <c r="B224" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>230</v>
+      </c>
+      <c r="B225" t="s">
         <v>231</v>
-      </c>
-      <c r="B225" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>232</v>
+      </c>
+      <c r="B226" t="s">
         <v>233</v>
-      </c>
-      <c r="B226" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>238</v>
+      </c>
+      <c r="B227" t="s">
         <v>239</v>
-      </c>
-      <c r="B227" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B228" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
+        <v>234</v>
+      </c>
+      <c r="B229" t="s">
         <v>235</v>
-      </c>
-      <c r="B229" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" t="s">
         <v>237</v>
-      </c>
-      <c r="B230" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>232</v>
+      </c>
+      <c r="B231" t="s">
         <v>233</v>
-      </c>
-      <c r="B231" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B232" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
+        <v>238</v>
+      </c>
+      <c r="B233" t="s">
         <v>239</v>
-      </c>
-      <c r="B233" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B234" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B235" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
+        <v>240</v>
+      </c>
+      <c r="B236" t="s">
         <v>241</v>
-      </c>
-      <c r="B236" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B237" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B238" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>242</v>
+      </c>
+      <c r="B239" t="s">
         <v>243</v>
-      </c>
-      <c r="B239" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B240" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B241" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
+        <v>244</v>
+      </c>
+      <c r="B242" t="s">
         <v>245</v>
-      </c>
-      <c r="B242" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B243" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
